--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/143.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/143.xlsx
@@ -426,13 +426,13 @@
         <v>-5.948164234060556</v>
       </c>
       <c r="E2">
-        <v>-9.055129645497233</v>
+        <v>-10.62828981644386</v>
       </c>
       <c r="F2">
-        <v>3.30910645283997</v>
+        <v>3.722755028897514</v>
       </c>
       <c r="G2">
-        <v>-13.34760763045117</v>
+        <v>-12.56442856168025</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.782525082915445</v>
       </c>
       <c r="E3">
-        <v>-10.63730147971913</v>
+        <v>-12.3693024049588</v>
       </c>
       <c r="F3">
-        <v>3.244962651371593</v>
+        <v>3.944571938549554</v>
       </c>
       <c r="G3">
-        <v>-12.80093062446024</v>
+        <v>-12.08180399078314</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.527941247152096</v>
       </c>
       <c r="E4">
-        <v>-12.139169884363</v>
+        <v>-13.50856231038649</v>
       </c>
       <c r="F4">
-        <v>3.434718429065681</v>
+        <v>3.979966420936372</v>
       </c>
       <c r="G4">
-        <v>-12.37614459467974</v>
+        <v>-10.97471783590438</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.18533529015709</v>
       </c>
       <c r="E5">
-        <v>-12.16705622730223</v>
+        <v>-14.83080426504211</v>
       </c>
       <c r="F5">
-        <v>3.580902081372515</v>
+        <v>4.354648594366227</v>
       </c>
       <c r="G5">
-        <v>-11.0532108706405</v>
+        <v>-10.50569629662814</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.746160918706254</v>
       </c>
       <c r="E6">
-        <v>-12.04596483233713</v>
+        <v>-16.22264433672161</v>
       </c>
       <c r="F6">
-        <v>3.402493280361975</v>
+        <v>3.644853701603443</v>
       </c>
       <c r="G6">
-        <v>-10.72279194145692</v>
+        <v>-10.53378958607439</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.203483050922484</v>
       </c>
       <c r="E7">
-        <v>-14.63460360018578</v>
+        <v>-16.99531521428037</v>
       </c>
       <c r="F7">
-        <v>3.890408307550106</v>
+        <v>3.859144065033647</v>
       </c>
       <c r="G7">
-        <v>-9.576638038669229</v>
+        <v>-9.648781447061026</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.558291957677997</v>
       </c>
       <c r="E8">
-        <v>-14.42268460204883</v>
+        <v>-16.31039710604225</v>
       </c>
       <c r="F8">
-        <v>3.57081919334564</v>
+        <v>4.052851155239089</v>
       </c>
       <c r="G8">
-        <v>-9.102094509433478</v>
+        <v>-8.089689956977878</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.812875290749816</v>
       </c>
       <c r="E9">
-        <v>-16.13931135803247</v>
+        <v>-18.57287253348845</v>
       </c>
       <c r="F9">
-        <v>3.784927315947228</v>
+        <v>4.69360328171334</v>
       </c>
       <c r="G9">
-        <v>-8.898290704944865</v>
+        <v>-7.517674035429367</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.990638775301858</v>
       </c>
       <c r="E10">
-        <v>-17.70812419393173</v>
+        <v>-19.32314557860526</v>
       </c>
       <c r="F10">
-        <v>4.025346043996534</v>
+        <v>4.284992836199622</v>
       </c>
       <c r="G10">
-        <v>-7.297933264714702</v>
+        <v>-7.200152991666789</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.117669731147855</v>
       </c>
       <c r="E11">
-        <v>-18.03741218139948</v>
+        <v>-20.31113633828073</v>
       </c>
       <c r="F11">
-        <v>4.328730635067436</v>
+        <v>4.104862687726064</v>
       </c>
       <c r="G11">
-        <v>-6.887634182214049</v>
+        <v>-5.309464018188081</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.2434976511408968</v>
       </c>
       <c r="E12">
-        <v>-18.35043389023168</v>
+        <v>-21.35142191579677</v>
       </c>
       <c r="F12">
-        <v>4.362587667554658</v>
+        <v>4.193829346786731</v>
       </c>
       <c r="G12">
-        <v>-5.80254660244375</v>
+        <v>-4.936014618085056</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.5939369633464928</v>
       </c>
       <c r="E13">
-        <v>-19.10562938659483</v>
+        <v>-21.70175825045217</v>
       </c>
       <c r="F13">
-        <v>4.017683645520639</v>
+        <v>4.233981971535229</v>
       </c>
       <c r="G13">
-        <v>-4.854806936006733</v>
+        <v>-4.097277974074083</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.348355660744027</v>
       </c>
       <c r="E14">
-        <v>-20.74130061274334</v>
+        <v>-23.74726995971687</v>
       </c>
       <c r="F14">
-        <v>4.2553372831794</v>
+        <v>4.686032003651753</v>
       </c>
       <c r="G14">
-        <v>-3.980021761618637</v>
+        <v>-3.574244884324628</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.001472785440315</v>
       </c>
       <c r="E15">
-        <v>-21.83010878925157</v>
+        <v>-24.78650040278913</v>
       </c>
       <c r="F15">
-        <v>4.560474699674626</v>
+        <v>4.571198744071268</v>
       </c>
       <c r="G15">
-        <v>-2.649685657753589</v>
+        <v>-1.655684427950797</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.538813173113259</v>
       </c>
       <c r="E16">
-        <v>-22.84677837481761</v>
+        <v>-25.40960936929655</v>
       </c>
       <c r="F16">
-        <v>4.632680172707047</v>
+        <v>4.774771690044052</v>
       </c>
       <c r="G16">
-        <v>-2.714843815057524</v>
+        <v>-1.671396277080178</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.969083109036888</v>
       </c>
       <c r="E17">
-        <v>-23.49079530581846</v>
+        <v>-26.87897238751337</v>
       </c>
       <c r="F17">
-        <v>4.566969100112575</v>
+        <v>4.918049429501866</v>
       </c>
       <c r="G17">
-        <v>-1.598150457023803</v>
+        <v>-1.290286274599279</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.299089851578549</v>
       </c>
       <c r="E18">
-        <v>-24.15172608723794</v>
+        <v>-26.94411901458772</v>
       </c>
       <c r="F18">
-        <v>4.978036483342995</v>
+        <v>4.936755622191884</v>
       </c>
       <c r="G18">
-        <v>-1.392946291772079</v>
+        <v>-0.315482898378721</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.541821410790904</v>
       </c>
       <c r="E19">
-        <v>-24.86613814668802</v>
+        <v>-26.73134413486332</v>
       </c>
       <c r="F19">
-        <v>4.900120245435674</v>
+        <v>5.107240260627245</v>
       </c>
       <c r="G19">
-        <v>-0.8281705333179533</v>
+        <v>-0.6941232338873237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.701816998188606</v>
       </c>
       <c r="E20">
-        <v>-25.4825495001381</v>
+        <v>-27.67023265087361</v>
       </c>
       <c r="F20">
-        <v>5.009628759350963</v>
+        <v>5.260536275454516</v>
       </c>
       <c r="G20">
-        <v>-0.6040929479468438</v>
+        <v>-0.007026128302667372</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.783516224032488</v>
       </c>
       <c r="E21">
-        <v>-27.44694718297741</v>
+        <v>-29.24991835286529</v>
       </c>
       <c r="F21">
-        <v>5.073823919598313</v>
+        <v>5.56440960329307</v>
       </c>
       <c r="G21">
-        <v>-0.606231560365213</v>
+        <v>0.5703330137462277</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.788136021659924</v>
       </c>
       <c r="E22">
-        <v>-26.86249327059946</v>
+        <v>-29.511288287166</v>
       </c>
       <c r="F22">
-        <v>5.179273433239885</v>
+        <v>5.74077068008389</v>
       </c>
       <c r="G22">
-        <v>-0.1216934941464035</v>
+        <v>0.3220487193919672</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.721733813659865</v>
       </c>
       <c r="E23">
-        <v>-27.4283442117539</v>
+        <v>-29.6772432741251</v>
       </c>
       <c r="F23">
-        <v>5.279093362012031</v>
+        <v>5.777644626652108</v>
       </c>
       <c r="G23">
-        <v>-0.6395356484902811</v>
+        <v>0.7200855412151598</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.595115350908346</v>
       </c>
       <c r="E24">
-        <v>-27.97911080598879</v>
+        <v>-29.8686505492443</v>
       </c>
       <c r="F24">
-        <v>5.117424209477263</v>
+        <v>5.551420802417174</v>
       </c>
       <c r="G24">
-        <v>-0.3922544494344198</v>
+        <v>0.6995734010538355</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.427400715838976</v>
       </c>
       <c r="E25">
-        <v>-27.94335850369823</v>
+        <v>-29.46294229866011</v>
       </c>
       <c r="F25">
-        <v>5.217244138249408</v>
+        <v>5.872840608581827</v>
       </c>
       <c r="G25">
-        <v>-0.8356192607813135</v>
+        <v>0.9707037701746065</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.240884611713713</v>
       </c>
       <c r="E26">
-        <v>-27.85077385261141</v>
+        <v>-29.92017779074058</v>
       </c>
       <c r="F26">
-        <v>5.016365043070528</v>
+        <v>5.954570650011637</v>
       </c>
       <c r="G26">
-        <v>0.0476111152774643</v>
+        <v>1.388203289223174</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.060447111172669</v>
       </c>
       <c r="E27">
-        <v>-28.03060861240402</v>
+        <v>-30.10066012231628</v>
       </c>
       <c r="F27">
-        <v>5.280127164530724</v>
+        <v>5.964580641707067</v>
       </c>
       <c r="G27">
-        <v>-0.2149350092599765</v>
+        <v>1.020259326351957</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.905053438672112</v>
       </c>
       <c r="E28">
-        <v>-27.55139643596432</v>
+        <v>-28.87002466836183</v>
       </c>
       <c r="F28">
-        <v>5.142512144638448</v>
+        <v>6.326998007371072</v>
       </c>
       <c r="G28">
-        <v>0.08774816939558817</v>
+        <v>0.4828584689620651</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.789083139337699</v>
       </c>
       <c r="E29">
-        <v>-26.48235957697358</v>
+        <v>-30.17345534198958</v>
       </c>
       <c r="F29">
-        <v>5.071015754102823</v>
+        <v>6.120611925698381</v>
       </c>
       <c r="G29">
-        <v>-0.05516808153474898</v>
+        <v>-0.06522551888305485</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.715219200512187</v>
       </c>
       <c r="E30">
-        <v>-26.10872877202273</v>
+        <v>-28.02998821146497</v>
       </c>
       <c r="F30">
-        <v>5.367644180636493</v>
+        <v>6.065525493412214</v>
       </c>
       <c r="G30">
-        <v>-1.037810829592301</v>
+        <v>0.4872052152551282</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.680239741770366</v>
       </c>
       <c r="E31">
-        <v>-26.16693777691732</v>
+        <v>-29.50915084743438</v>
       </c>
       <c r="F31">
-        <v>5.016974721478989</v>
+        <v>6.112406118206249</v>
       </c>
       <c r="G31">
-        <v>-0.4089462200434251</v>
+        <v>-0.06997284118636972</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.669360653144523</v>
       </c>
       <c r="E32">
-        <v>-25.15118747157484</v>
+        <v>-28.57495835897004</v>
       </c>
       <c r="F32">
-        <v>5.146839535950673</v>
+        <v>5.559412891119384</v>
       </c>
       <c r="G32">
-        <v>-0.6157162733352249</v>
+        <v>-0.003884420585899016</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.666434213159</v>
       </c>
       <c r="E33">
-        <v>-26.57205506164351</v>
+        <v>-27.92713298132875</v>
       </c>
       <c r="F33">
-        <v>5.433378447518244</v>
+        <v>5.671519165209852</v>
       </c>
       <c r="G33">
-        <v>-0.1523027982025049</v>
+        <v>-0.4268397186831859</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.649453793978513</v>
       </c>
       <c r="E34">
-        <v>-24.71684794407715</v>
+        <v>-27.10359828371584</v>
       </c>
       <c r="F34">
-        <v>5.356240874969554</v>
+        <v>5.350493661928931</v>
       </c>
       <c r="G34">
-        <v>-1.003768489811976</v>
+        <v>-0.1898907322553899</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.602691334891557</v>
       </c>
       <c r="E35">
-        <v>-24.55428025567579</v>
+        <v>-25.97432819194908</v>
       </c>
       <c r="F35">
-        <v>5.322287751863608</v>
+        <v>6.017395690574757</v>
       </c>
       <c r="G35">
-        <v>-0.9056637833012133</v>
+        <v>-0.7543552994288237</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.511878538820179</v>
       </c>
       <c r="E36">
-        <v>-24.161204183336</v>
+        <v>-26.61646580623673</v>
       </c>
       <c r="F36">
-        <v>5.481932374465934</v>
+        <v>5.890082247703695</v>
       </c>
       <c r="G36">
-        <v>-1.385411490124697</v>
+        <v>-0.8732535424717484</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.372385635201744</v>
       </c>
       <c r="E37">
-        <v>-23.15516745473996</v>
+        <v>-26.79443030626417</v>
       </c>
       <c r="F37">
-        <v>5.46506184394052</v>
+        <v>5.810254137830713</v>
       </c>
       <c r="G37">
-        <v>-0.778396481135011</v>
+        <v>-1.148621409882786</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.18361325269764</v>
       </c>
       <c r="E38">
-        <v>-22.70796253258649</v>
+        <v>-24.61394290072685</v>
       </c>
       <c r="F38">
-        <v>5.801541369488068</v>
+        <v>6.009343959419546</v>
       </c>
       <c r="G38">
-        <v>-1.811001982471244</v>
+        <v>-0.02444621893031236</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.952202884834913</v>
       </c>
       <c r="E39">
-        <v>-22.17133383420354</v>
+        <v>-24.10550848151566</v>
       </c>
       <c r="F39">
-        <v>5.729597660554931</v>
+        <v>6.26662824778985</v>
       </c>
       <c r="G39">
-        <v>-1.736829209663873</v>
+        <v>-0.9871594828414521</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.688370985132872</v>
       </c>
       <c r="E40">
-        <v>-21.49773238251059</v>
+        <v>-23.07954193881187</v>
       </c>
       <c r="F40">
-        <v>5.918468741862829</v>
+        <v>6.316926716487836</v>
       </c>
       <c r="G40">
-        <v>-2.239714319261323</v>
+        <v>-0.5260567684951434</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.406844294181093</v>
       </c>
       <c r="E41">
-        <v>-20.69376069261082</v>
+        <v>-22.54106109455979</v>
       </c>
       <c r="F41">
-        <v>6.06432601741296</v>
+        <v>6.19323655263662</v>
       </c>
       <c r="G41">
-        <v>-2.208485943189379</v>
+        <v>-1.893295523486447</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.123437918467663</v>
       </c>
       <c r="E42">
-        <v>-20.45501048597842</v>
+        <v>-23.27233719121443</v>
       </c>
       <c r="F42">
-        <v>6.050664582205991</v>
+        <v>6.191268351687568</v>
       </c>
       <c r="G42">
-        <v>-2.519899030432001</v>
+        <v>-0.7797869102615049</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.852245041455486</v>
       </c>
       <c r="E43">
-        <v>-18.38878100812863</v>
+        <v>-20.9758348100746</v>
       </c>
       <c r="F43">
-        <v>6.120891913880528</v>
+        <v>6.139440716764014</v>
       </c>
       <c r="G43">
-        <v>-3.036195160009039</v>
+        <v>-1.794389664955181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.6045013013719279</v>
       </c>
       <c r="E44">
-        <v>-18.68097173652555</v>
+        <v>-21.33739270332101</v>
       </c>
       <c r="F44">
-        <v>5.94372069376977</v>
+        <v>6.408335402651956</v>
       </c>
       <c r="G44">
-        <v>-3.250701958226116</v>
+        <v>-1.633040296462182</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.3853622092182509</v>
       </c>
       <c r="E45">
-        <v>-17.28964791088291</v>
+        <v>-19.95120869567708</v>
       </c>
       <c r="F45">
-        <v>6.512956548890728</v>
+        <v>6.301085018276699</v>
       </c>
       <c r="G45">
-        <v>-2.463513818807134</v>
+        <v>-2.203205623054241</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.1963180355799983</v>
       </c>
       <c r="E46">
-        <v>-17.43087742976013</v>
+        <v>-18.89357453423765</v>
       </c>
       <c r="F46">
-        <v>6.357677422501155</v>
+        <v>6.435461121624028</v>
       </c>
       <c r="G46">
-        <v>-3.824131482719896</v>
+        <v>-1.353669979494165</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.03188571461553387</v>
       </c>
       <c r="E47">
-        <v>-15.86906108620271</v>
+        <v>-17.96554982737176</v>
       </c>
       <c r="F47">
-        <v>6.205561002855471</v>
+        <v>6.749644310157825</v>
       </c>
       <c r="G47">
-        <v>-3.864314884475569</v>
+        <v>-2.999875164897695</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1135237398804461</v>
       </c>
       <c r="E48">
-        <v>-15.9011724953911</v>
+        <v>-18.30530764674524</v>
       </c>
       <c r="F48">
-        <v>6.537648524433376</v>
+        <v>7.119863240021397</v>
       </c>
       <c r="G48">
-        <v>-3.651039609199102</v>
+        <v>-3.351051214612504</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2497270744971292</v>
       </c>
       <c r="E49">
-        <v>-14.95603921372423</v>
+        <v>-17.44890528478466</v>
       </c>
       <c r="F49">
-        <v>6.267731633170379</v>
+        <v>6.801175389551177</v>
       </c>
       <c r="G49">
-        <v>-4.238389977685517</v>
+        <v>-3.178349985465344</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3821388829288408</v>
       </c>
       <c r="E50">
-        <v>-14.62143932624548</v>
+        <v>-16.92615183076122</v>
       </c>
       <c r="F50">
-        <v>6.790028877779107</v>
+        <v>6.91142777739418</v>
       </c>
       <c r="G50">
-        <v>-4.240773570473793</v>
+        <v>-3.567623793246086</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5178105397969158</v>
       </c>
       <c r="E51">
-        <v>-14.14989838477478</v>
+        <v>-15.72981956741486</v>
       </c>
       <c r="F51">
-        <v>6.700111252940026</v>
+        <v>6.57180542592041</v>
       </c>
       <c r="G51">
-        <v>-4.533230473958549</v>
+        <v>-3.585510670794768</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.6565388494027851</v>
       </c>
       <c r="E52">
-        <v>-13.09312916187082</v>
+        <v>-16.2151361268169</v>
       </c>
       <c r="F52">
-        <v>6.778705095382837</v>
+        <v>6.466697199648793</v>
       </c>
       <c r="G52">
-        <v>-5.289653713681083</v>
+        <v>-4.295957054067904</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8002540956524101</v>
       </c>
       <c r="E53">
-        <v>-11.98091330321694</v>
+        <v>-13.90078250113883</v>
       </c>
       <c r="F53">
-        <v>6.551273511474622</v>
+        <v>6.96390816583114</v>
       </c>
       <c r="G53">
-        <v>-4.610220521019839</v>
+        <v>-3.611759986375649</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.9448151600096595</v>
       </c>
       <c r="E54">
-        <v>-11.45633487416841</v>
+        <v>-13.57890309714763</v>
       </c>
       <c r="F54">
-        <v>6.860191596796224</v>
+        <v>6.630460464977838</v>
       </c>
       <c r="G54">
-        <v>-5.593273776724261</v>
+        <v>-4.643077685497106</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.089823873774663</v>
       </c>
       <c r="E55">
-        <v>-12.18194132136545</v>
+        <v>-12.70807754547262</v>
       </c>
       <c r="F55">
-        <v>6.552019042137141</v>
+        <v>7.025149367920107</v>
       </c>
       <c r="G55">
-        <v>-5.728161954721866</v>
+        <v>-4.585103412013389</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.230485764129332</v>
       </c>
       <c r="E56">
-        <v>-9.557609121388337</v>
+        <v>-12.89578732156456</v>
       </c>
       <c r="F56">
-        <v>6.626751035748102</v>
+        <v>7.362924460085633</v>
       </c>
       <c r="G56">
-        <v>-5.841104526339642</v>
+        <v>-5.93409112944669</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.365420558500325</v>
       </c>
       <c r="E57">
-        <v>-9.94083123428744</v>
+        <v>-12.15579844091917</v>
       </c>
       <c r="F57">
-        <v>6.778746513752977</v>
+        <v>7.093569201921735</v>
       </c>
       <c r="G57">
-        <v>-6.609746989647626</v>
+        <v>-5.062679400963111</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.490419415409789</v>
       </c>
       <c r="E58">
-        <v>-9.836889170389382</v>
+        <v>-13.02434617016832</v>
       </c>
       <c r="F58">
-        <v>6.898743815722514</v>
+        <v>6.877164844879586</v>
       </c>
       <c r="G58">
-        <v>-6.798365321747601</v>
+        <v>-5.248136162073083</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.605095268023777</v>
       </c>
       <c r="E59">
-        <v>-8.865015249707216</v>
+        <v>-11.2161627266976</v>
       </c>
       <c r="F59">
-        <v>6.818695360120386</v>
+        <v>6.996441467208688</v>
       </c>
       <c r="G59">
-        <v>-7.031149641886994</v>
+        <v>-7.165087693314828</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.707901555033351</v>
       </c>
       <c r="E60">
-        <v>-8.647458301430717</v>
+        <v>-10.3956983344619</v>
       </c>
       <c r="F60">
-        <v>6.723666708406032</v>
+        <v>7.224461191972891</v>
       </c>
       <c r="G60">
-        <v>-7.200685989498611</v>
+        <v>-5.529370316179709</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.800778343523976</v>
       </c>
       <c r="E61">
-        <v>-8.460753846568476</v>
+        <v>-10.78519238386162</v>
       </c>
       <c r="F61">
-        <v>6.516954249976639</v>
+        <v>7.271688074341296</v>
       </c>
       <c r="G61">
-        <v>-7.148578002710482</v>
+        <v>-7.469836652386898</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.884236210084185</v>
       </c>
       <c r="E62">
-        <v>-8.299146194656744</v>
+        <v>-9.420174463729548</v>
       </c>
       <c r="F62">
-        <v>6.798577629375997</v>
+        <v>7.044206788388912</v>
       </c>
       <c r="G62">
-        <v>-8.031457460942098</v>
+        <v>-7.465003255899562</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.960393116129288</v>
       </c>
       <c r="E63">
-        <v>-8.405184942020353</v>
+        <v>-10.39354278083425</v>
       </c>
       <c r="F63">
-        <v>6.852759484458308</v>
+        <v>6.95717353884638</v>
       </c>
       <c r="G63">
-        <v>-8.15967820022361</v>
+        <v>-7.678516890454858</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.029726399993672</v>
       </c>
       <c r="E64">
-        <v>-7.155194790157112</v>
+        <v>-9.069820015178117</v>
       </c>
       <c r="F64">
-        <v>6.358537267865261</v>
+        <v>7.089810070647831</v>
       </c>
       <c r="G64">
-        <v>-8.384033871420018</v>
+        <v>-8.161667838092711</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.093523433813</v>
       </c>
       <c r="E65">
-        <v>-7.815102136450867</v>
+        <v>-9.661184378891774</v>
       </c>
       <c r="F65">
-        <v>6.929337080642705</v>
+        <v>7.044296252068415</v>
       </c>
       <c r="G65">
-        <v>-9.08719043341568</v>
+        <v>-8.50299170428265</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.15131150545703</v>
       </c>
       <c r="E66">
-        <v>-7.450211286334813</v>
+        <v>-9.338797785811712</v>
       </c>
       <c r="F66">
-        <v>6.601373171995936</v>
+        <v>6.963339905792819</v>
       </c>
       <c r="G66">
-        <v>-9.041137434418877</v>
+        <v>-8.287508295131488</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.20291413678774</v>
       </c>
       <c r="E67">
-        <v>-7.490075443024335</v>
+        <v>-9.076082894730725</v>
       </c>
       <c r="F67">
-        <v>6.633449214567139</v>
+        <v>6.681499494133926</v>
       </c>
       <c r="G67">
-        <v>-8.67555057997162</v>
+        <v>-8.07237249326195</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.246029146993578</v>
       </c>
       <c r="E68">
-        <v>-7.008725826853022</v>
+        <v>-8.16646643470601</v>
       </c>
       <c r="F68">
-        <v>6.413678372400013</v>
+        <v>6.826707329640263</v>
       </c>
       <c r="G68">
-        <v>-9.141754844993947</v>
+        <v>-7.828471361201685</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.277877844656463</v>
       </c>
       <c r="E69">
-        <v>-6.719560119093231</v>
+        <v>-8.320855699049515</v>
       </c>
       <c r="F69">
-        <v>6.618475645394135</v>
+        <v>6.829918081693514</v>
       </c>
       <c r="G69">
-        <v>-9.287316221810162</v>
+        <v>-7.688163820156293</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.292483122558473</v>
       </c>
       <c r="E70">
-        <v>-7.436354155871341</v>
+        <v>-9.760779107742467</v>
       </c>
       <c r="F70">
-        <v>6.456897613273674</v>
+        <v>6.996414959451798</v>
       </c>
       <c r="G70">
-        <v>-8.749299602949966</v>
+        <v>-8.660226064670335</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.284141973224472</v>
       </c>
       <c r="E71">
-        <v>-7.213793243816366</v>
+        <v>-7.971932248284507</v>
       </c>
       <c r="F71">
-        <v>6.312397203529328</v>
+        <v>6.493508139007801</v>
       </c>
       <c r="G71">
-        <v>-9.23776397617835</v>
+        <v>-8.260831919176042</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.245474364200897</v>
       </c>
       <c r="E72">
-        <v>-6.450274412227113</v>
+        <v>-8.90501073214296</v>
       </c>
       <c r="F72">
-        <v>6.208183614052734</v>
+        <v>6.333046746146315</v>
       </c>
       <c r="G72">
-        <v>-9.417202165497928</v>
+        <v>-9.229053930864529</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.172822164371413</v>
       </c>
       <c r="E73">
-        <v>-6.325220602505296</v>
+        <v>-8.301043625265958</v>
       </c>
       <c r="F73">
-        <v>6.16129139211506</v>
+        <v>6.291237386592218</v>
       </c>
       <c r="G73">
-        <v>-8.7367923619026</v>
+        <v>-8.866641889589433</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.061034616575</v>
       </c>
       <c r="E74">
-        <v>-7.085818568359602</v>
+        <v>-9.223385097252226</v>
       </c>
       <c r="F74">
-        <v>6.225443477257464</v>
+        <v>6.326542405299532</v>
       </c>
       <c r="G74">
-        <v>-8.455634350343376</v>
+        <v>-8.545836784651897</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.910303995555817</v>
       </c>
       <c r="E75">
-        <v>-7.650039258871282</v>
+        <v>-8.023353070641603</v>
       </c>
       <c r="F75">
-        <v>5.833889116567389</v>
+        <v>6.12086871959325</v>
       </c>
       <c r="G75">
-        <v>-7.97235098088395</v>
+        <v>-7.683538988037932</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.719680491494243</v>
       </c>
       <c r="E76">
-        <v>-7.687317656902425</v>
+        <v>-9.040824196107003</v>
       </c>
       <c r="F76">
-        <v>6.083890398732279</v>
+        <v>6.311635105518753</v>
       </c>
       <c r="G76">
-        <v>-7.948405804998401</v>
+        <v>-7.954745499706106</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.494161044006987</v>
       </c>
       <c r="E77">
-        <v>-8.06956614788988</v>
+        <v>-9.28476403395219</v>
       </c>
       <c r="F77">
-        <v>6.13707821293123</v>
+        <v>5.832393085037933</v>
       </c>
       <c r="G77">
-        <v>-8.444841971885351</v>
+        <v>-7.355033554176051</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.237793175862677</v>
       </c>
       <c r="E78">
-        <v>-7.442879686916394</v>
+        <v>-9.198718499332445</v>
       </c>
       <c r="F78">
-        <v>5.508847688117696</v>
+        <v>5.777129382127566</v>
       </c>
       <c r="G78">
-        <v>-7.77380101216616</v>
+        <v>-7.084710958166863</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.9597062020189724</v>
       </c>
       <c r="E79">
-        <v>-8.135419216909423</v>
+        <v>-10.30007054884192</v>
       </c>
       <c r="F79">
-        <v>5.965839760159322</v>
+        <v>5.80127297844956</v>
       </c>
       <c r="G79">
-        <v>-7.584735756418383</v>
+        <v>-6.989502979002963</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.6666651540814799</v>
       </c>
       <c r="E80">
-        <v>-9.250555941298247</v>
+        <v>-10.06511520342795</v>
       </c>
       <c r="F80">
-        <v>5.785222531652917</v>
+        <v>6.015531863918459</v>
       </c>
       <c r="G80">
-        <v>-7.11883937213121</v>
+        <v>-6.805026139372615</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3668000218000681</v>
       </c>
       <c r="E81">
-        <v>-9.546799653932027</v>
+        <v>-11.74817691006673</v>
       </c>
       <c r="F81">
-        <v>5.751890684099071</v>
+        <v>5.88051129073175</v>
       </c>
       <c r="G81">
-        <v>-7.405949744570043</v>
+        <v>-5.895774875375166</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.06515880962223024</v>
       </c>
       <c r="E82">
-        <v>-10.95212099273237</v>
+        <v>-11.85766635462419</v>
       </c>
       <c r="F82">
-        <v>5.694312522665283</v>
+        <v>6.013769098085301</v>
       </c>
       <c r="G82">
-        <v>-6.610766637673721</v>
+        <v>-5.465778046915849</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.2330148895787474</v>
       </c>
       <c r="E83">
-        <v>-11.17183802311053</v>
+        <v>-10.9399756254438</v>
       </c>
       <c r="F83">
-        <v>5.668691118896694</v>
+        <v>5.713598572537261</v>
       </c>
       <c r="G83">
-        <v>-6.82339966711557</v>
+        <v>-6.252972807425909</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.5240308395673289</v>
       </c>
       <c r="E84">
-        <v>-11.58678209643336</v>
+        <v>-13.36092500078842</v>
       </c>
       <c r="F84">
-        <v>5.601648031518519</v>
+        <v>5.816077560672394</v>
       </c>
       <c r="G84">
-        <v>-6.31751520325954</v>
+        <v>-6.491699556808293</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.8054678841022849</v>
       </c>
       <c r="E85">
-        <v>-12.62771977420651</v>
+        <v>-13.77501772099781</v>
       </c>
       <c r="F85">
-        <v>5.382992171875562</v>
+        <v>5.562842332166974</v>
       </c>
       <c r="G85">
-        <v>-6.227686860596956</v>
+        <v>-4.921746166810797</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.075301928483611</v>
       </c>
       <c r="E86">
-        <v>-14.16081653560728</v>
+        <v>-15.45542121339409</v>
       </c>
       <c r="F86">
-        <v>5.695710806841208</v>
+        <v>5.252728084315728</v>
       </c>
       <c r="G86">
-        <v>-5.421281004322505</v>
+        <v>-4.067453269310789</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.332552693679288</v>
       </c>
       <c r="E87">
-        <v>-14.74372623834861</v>
+        <v>-16.72481587638019</v>
       </c>
       <c r="F87">
-        <v>5.540529427805166</v>
+        <v>5.710101205362641</v>
       </c>
       <c r="G87">
-        <v>-5.038111842516179</v>
+        <v>-5.119382424959748</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.572966189555177</v>
       </c>
       <c r="E88">
-        <v>-16.84907267467666</v>
+        <v>-17.79448672173201</v>
       </c>
       <c r="F88">
-        <v>5.431653786585616</v>
+        <v>5.503024265276015</v>
       </c>
       <c r="G88">
-        <v>-4.273931994595133</v>
+        <v>-3.446236019957629</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.792427467796589</v>
       </c>
       <c r="E89">
-        <v>-17.86828726263501</v>
+        <v>-19.13743738802471</v>
       </c>
       <c r="F89">
-        <v>5.23909647033526</v>
+        <v>5.16207155575335</v>
       </c>
       <c r="G89">
-        <v>-3.884135120619186</v>
+        <v>-3.725354735464661</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.983027385370651</v>
       </c>
       <c r="E90">
-        <v>-19.01584786091876</v>
+        <v>-20.79020813202618</v>
       </c>
       <c r="F90">
-        <v>4.785576914446169</v>
+        <v>5.05279664144565</v>
       </c>
       <c r="G90">
-        <v>-4.189403835340921</v>
+        <v>-4.429626951307057</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.137337302005067</v>
       </c>
       <c r="E91">
-        <v>-20.11368581459828</v>
+        <v>-21.92113564527975</v>
       </c>
       <c r="F91">
-        <v>5.068323560043725</v>
+        <v>4.464178645833989</v>
       </c>
       <c r="G91">
-        <v>-3.379425900429597</v>
+        <v>-3.728552722455597</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.245740306493287</v>
       </c>
       <c r="E92">
-        <v>-22.41265168559829</v>
+        <v>-23.7708451954008</v>
       </c>
       <c r="F92">
-        <v>4.770570210577054</v>
+        <v>4.428063483806736</v>
       </c>
       <c r="G92">
-        <v>-2.678086827934996</v>
+        <v>-2.704425528245438</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.298740291727779</v>
       </c>
       <c r="E93">
-        <v>-24.96369053376125</v>
+        <v>-25.46466655628181</v>
       </c>
       <c r="F93">
-        <v>4.765952890673849</v>
+        <v>3.946419197857797</v>
       </c>
       <c r="G93">
-        <v>-2.693888061793938</v>
+        <v>-3.375055980317759</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.287234746407398</v>
       </c>
       <c r="E94">
-        <v>-27.19837018774837</v>
+        <v>-26.26199497481233</v>
       </c>
       <c r="F94">
-        <v>4.314986363120187</v>
+        <v>3.739430064715868</v>
       </c>
       <c r="G94">
-        <v>-2.531740851825974</v>
+        <v>-2.622297514507198</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.205709927124665</v>
       </c>
       <c r="E95">
-        <v>-29.37147618065319</v>
+        <v>-28.96108322370806</v>
       </c>
       <c r="F95">
-        <v>3.794496616184368</v>
+        <v>3.575820875723744</v>
       </c>
       <c r="G95">
-        <v>-3.016765568239057</v>
+        <v>-1.813868914908253</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.045502980189006</v>
       </c>
       <c r="E96">
-        <v>-30.85781191945075</v>
+        <v>-32.68423832046136</v>
       </c>
       <c r="F96">
-        <v>3.330637378373535</v>
+        <v>3.406681505950529</v>
       </c>
       <c r="G96">
-        <v>-2.366614150872667</v>
+        <v>-2.85463491099879</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.813027932839853</v>
       </c>
       <c r="E97">
-        <v>-33.72672020787113</v>
+        <v>-33.99998870762699</v>
       </c>
       <c r="F97">
-        <v>3.373695915971053</v>
+        <v>2.999734422181633</v>
       </c>
       <c r="G97">
-        <v>-3.003536628264129</v>
+        <v>-2.106901853316842</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.495957330792138</v>
       </c>
       <c r="E98">
-        <v>-35.74161037589596</v>
+        <v>-35.40845960009967</v>
       </c>
       <c r="F98">
-        <v>2.969300203802779</v>
+        <v>2.409053791737001</v>
       </c>
       <c r="G98">
-        <v>-2.890239828273651</v>
+        <v>-1.812554628329162</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.121447288018563</v>
       </c>
       <c r="E99">
-        <v>-38.27321754209201</v>
+        <v>-38.903148654692</v>
       </c>
       <c r="F99">
-        <v>2.567041679533728</v>
+        <v>2.526348959238605</v>
       </c>
       <c r="G99">
-        <v>-3.057697153286605</v>
+        <v>-2.407734437015954</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.6599392310191543</v>
       </c>
       <c r="E100">
-        <v>-40.51424838087488</v>
+        <v>-42.07428503414729</v>
       </c>
       <c r="F100">
-        <v>2.191444988491182</v>
+        <v>1.731237194191888</v>
       </c>
       <c r="G100">
-        <v>-2.895139435671772</v>
+        <v>-2.318144453632197</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.177537576180596</v>
       </c>
       <c r="E101">
-        <v>-44.41750315315024</v>
+        <v>-43.8106219732493</v>
       </c>
       <c r="F101">
-        <v>1.868988066338224</v>
+        <v>1.79070734677367</v>
       </c>
       <c r="G101">
-        <v>-3.138037472433639</v>
+        <v>-1.742682254177305</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4158914494056028</v>
       </c>
       <c r="E102">
-        <v>-45.70838768953975</v>
+        <v>-46.36744368272007</v>
       </c>
       <c r="F102">
-        <v>1.519117153357019</v>
+        <v>1.474115265832533</v>
       </c>
       <c r="G102">
-        <v>-3.460107205767176</v>
+        <v>-1.772665865126484</v>
       </c>
     </row>
   </sheetData>
